--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.152.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.152.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.152.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.152.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="53" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.152.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.152.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0152.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0152.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -602,11 +602,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: onlyâ€”namely in what cases leave can be obtained to file</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]#</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]#</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L29: isolated marker/symbol line :: 145</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 145</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]#</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -659,11 +663,7 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a claim,â€”that nearly all the English decisions since the</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: /</t>
+          <t>L5: isolated marker/symbol line :: 145</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -718,7 +718,11 @@
           <t>L71: symbol-only separator/garbage line :: 1, 1850,</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L54: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -743,7 +747,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -942,7 +946,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -981,7 +985,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1020,7 +1024,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
